--- a/DISASTER/intervention_type.xlsx
+++ b/DISASTER/intervention_type.xlsx
@@ -25,10 +25,10 @@
     <t>Livelihood Enhancement</t>
   </si>
   <si>
-    <t xml:space="preserve"> Civil Engineering </t>
+    <t>Civil Engineering</t>
   </si>
   <si>
-    <t xml:space="preserve"> Bioremediation</t>
+    <t>Bioremediation</t>
   </si>
 </sst>
 </file>
